--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>48984</t>
   </si>
@@ -67,6 +67,9 @@
     <t>436503</t>
   </si>
   <si>
+    <t>571937</t>
+  </si>
+  <si>
     <t>436513</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>Denominación del área responsable de la elaboración y/o presentación del informe</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Descripción de la temática que se aborda en el informe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fundamento legal </t>
   </si>
   <si>
@@ -133,79 +139,40 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>A73D2CC38A18C415719F810575E387EF</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>Informe Actividades</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>Ley que crea Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Mensual</t>
-  </si>
-  <si>
-    <t>15/08/2022</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/photo/?fbid=186867177192786&amp;set=a.147087684504069&amp;__cft__[0]=AZWOpiWNujlDk9vlXyxjv6CXz_547ngUWtG34XnSDN160OYqUEmTBpRb9rnW-uDd9ESAvrBCmuiLWBcL6p4_ZIylP8FQ7Awfj_8VIw4dLozUvYveDQXxkrjyZ3eL8X3Zo3zz2ZRrwYbvQjVlg_xbGP8QjH71-GKXOcX_5kM6UzL2UcsJ2VVGAlWEKiS_t_p9CCBAl6uQ9njYf4h3RSeJlyIG&amp;__tn__=EH-y-R</t>
-  </si>
-  <si>
-    <t>Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>F29E56DFB20CDBE08AB87C721E33156A</t>
-  </si>
-  <si>
-    <t>https://fb.watch/fcUrkrCInL/</t>
-  </si>
-  <si>
-    <t>FFF67072D28C001C0DD1C5C2D10EAEF0</t>
-  </si>
-  <si>
-    <t>https://m.facebook.com/story.php?story_fbid=182563757623128&amp;id=100076085146677&amp;sfnsn=scwspmo</t>
-  </si>
-  <si>
-    <t>5AB4FA3FA9D8D76201EB227976E66CD1</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/100077564144492/videos/472181698115731/?sfnsn=scwspmo</t>
-  </si>
-  <si>
-    <t>D1C4BB8C80F5E0D6F0232441A9274E5E</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/photo/?fbid=456601903148747&amp;set=a.440950094713928&amp;__cft__[0]=AZU6uwvekQlE0OX0AwFq71FODw_fztHmoY8hVWlZe-JUDXUEouxlBJISX7ja0pIWWCDlAi1Uf1YOkeWgB1Q-dL6uE7HgPqFlizkBP2xkVkdXdh6GLHShMIWUURNzmceinKz0CXtThgSlPGWTm-6bhtUX5a1_1fyhW0rqG7gP4RiHLgiiimOkpbc_CcSNUL5KX7w&amp;__tn__=EH-R</t>
-  </si>
-  <si>
-    <t>995B9C23C42DAEE2F8BCEFD53E845973</t>
-  </si>
-  <si>
-    <t>https://fb.watch/f_Nsq9QGfA/</t>
-  </si>
-  <si>
-    <t>7B6E9947F97DABECDE9784DA6410F12B</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/TiaxcaGuerrerosJaguar?__cft__[0]=AZWb937NxAAgDZmAJzQWuPjYt8QvpZC7t2S6IRTtNGOWf-SggMa1uTaX95WAONEuPg8ukjnBrN7QtYiA4aXXMnqsTRvXB_5U6Gj9ywV7Y5KpslcEGNTDhAqqCMR470Sel6fJrc33MAOkHod9tdDMWI8M_CZ1DHrobdRl-QEcvJBI8ghXU1DudwaSJJazVuR5rVPGJawI7UQPRN8-8uBbgU54&amp;__tn__=-]C%2CP-y-R</t>
+    <t>Ley de General de Transparencia, Ley de Transparencia del Estado de Tlaxcala, Ley General de Archivos y Ley de Archivos del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>Área de Transparencia y Archivo</t>
+  </si>
+  <si>
+    <t>Informe de actividades</t>
+  </si>
+  <si>
+    <t>11CCCEDC4064E78828FE17903664494A</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>Transparencia y Archivo</t>
+  </si>
+  <si>
+    <t>11/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de julio del 2023, al 30 de septiembre del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, no ha generado informes, lo anterior por motivo de que estos son efectuados de forma anual de acuerdo al artículo 63, fracción XXIX, de la LEY DE TRANSPARENCIA Y ACCESO A LA INFORMACIÓN PÚBLICA DEL ESTADO DE TLAXCALA; mismo que generaliza todas las actividades efectuadas durante el ejercicio, las cuales son planeadas mediante el Plan Anual de Trabajo.</t>
   </si>
 </sst>
 </file>
@@ -598,31 +565,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="101.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="231.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="123" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -639,7 +607,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -654,7 +622,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -674,28 +642,31 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>9</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>7</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>10</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -735,10 +706,13 @@
       <c r="N5" t="s">
         <v>24</v>
       </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -753,359 +727,102 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="J8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>51</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="A6:O6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
